--- a/output/(山本)保守性_持続可能性_再構成.xlsx
+++ b/output/(山本)保守性_持続可能性_再構成.xlsx
@@ -461,13 +461,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>採用するシステム構成やアーキテクチャが、既存の技術的知見や物理法則に照らし、理論的・技術的に実現可能であることを、実証データや文献などの客観的根拠に基づき確認している。</t>
+          <t>要求事項およびアーキテクチャ設計において、現行の技術水準および物理法則と矛盾しないシステム仕様を、実証済みの技術要素に基づき明記している。</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】永久機関を電源として利用し、外部からのエネルギー供給なしに稼働し続けるシステムを要求する。（物理法則に反し、技術的に実現不可能であるため）
-→【適合例】実証済みのシステム構成と、信頼性の高い冗長化電源アーキテクチャに基づき、電源ユニットの設計を行う。</t>
+          <t>★新規追加
+【非適合例】外部からのエネルギー供給なしに永続稼働するサーバー環境を構築する。（永久機関を要求しており物理的および理論的に実現不可能である。）
+→【適合例】実証済みのシステム構成およびアーキテクチャを採用し、冗長電源およびUPSを備えた構成とする。</t>
         </is>
       </c>
     </row>
@@ -479,14 +480,14 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>定められた納期、予算、およびハードウェア・ソフトウェアの物理的・論理的制約条件下において、すべての要求事項が矛盾なく達成可能であることを、リソース計画やフィジビリティスタディに基づき確認している。</t>
+          <t>ハードウェア性能およびネットワーク帯域等のリソース制約を考慮し、論理的および物理的に達成可能な要件を運用環境の上限値に基づき明記している。</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】10Gbpsの通信帯域を必須要件としているが、接続するネットワーク機器の物理上限が100Mbpsである制約を見落としている。（物理的な制約により実現不可能であるため）
-→【適合例】ネットワーク機器の仕様に基づき、実現可能な最大通信速度の範囲内でスループット要件を定義する。</t>
+【非適合例】利用可能なネットワーク帯域が10Mbpsの環境下で、毎秒1GBのログデータを外部転送する。（通信帯域の上限を超過しており物理的に実現不可能である。）
+→【適合例】利用可能なネットワーク帯域が10Mbpsの環境であることを前提とし、ログデータはローカルで圧縮および蓄積した上で、夜間のバッチ処理により差分転送する設計とする。</t>
         </is>
       </c>
     </row>
@@ -498,13 +499,14 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>製品のライフサイクル全般を見据え、採用するハードウェア部品のEOL（販売終了）情報やソフトウェアライブラリのサポート継続性を確認し、将来にわたる調達および保守が可能であることを明記している。</t>
+          <t>開発対象システムを構成するハードウェアおよびソフトウェアコンポーネントについて、市場で調達可能であること、およびベンダーの保守サポートが継続していることを要件として明記している。</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】既にメーカーから販売中止（ディスコン）が公表されている型番のマイコンを使用した開発を要求している。（将来的な部品調達および保守が不可能であるため）
-→【適合例】メーカーの長期供給ロードマップを確認し、開発および保守期間を通じて安定供給が保証されている現行製品のマイコンを採用する。</t>
+          <t>★新規追加
+【非適合例】本デバイスの制御基板には、製造終了（ディスコン）である型番Xのマイコンを使用した開発を要求する。（製造終了製品を指定しており部品の調達および保守が不可能である。）
+→【適合例】本デバイスの制御基板には、メーカーサポート期間が今後5年以上保証されている現行製品のマイコンを指定する。</t>
         </is>
       </c>
     </row>
@@ -516,13 +518,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>記述された仕様、数値、および技術的情報が、引用元の公的規格、上位設計書、または外部インタフェース仕様書等の客観的事実と完全に一致しており、第三者が成否を客観的に判定できる状態であることを確認している。</t>
+          <t>システムの仕様および要件について、プロトコルや数値基準などの具体的な指標を記載し、第三者がテストやログ解析により客観的に成否を判定できる形で定義している。</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】既存システムのAPI仕様とは異なるデータ型や、実在しないパラメータ名が連携仕様書に記載されている。（事実と異なる情報が含まれ、実装後のテストで検証ができないため）
-→【適合例】最新のAPI定義書と照合し、整合性の取れたデータ型およびパラメータ名を正確に記述する。</t>
+          <t>★新規追加
+【非適合例】ユーザー認証機能は、既存システムと同じ方法で連携する。（連携プロトコルや対象が不明確であり、テストによる成否の検証が不可能である。）
+→【適合例】ユーザー認証機能は、既存のActive Directoryサーバーに対してLDAPプロトコルを用いて連携する。</t>
         </is>
       </c>
     </row>
@@ -534,13 +537,14 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>文書内の未決定事項（TBD）に対して、解消の期限（いつまでに）、決定の権限者（誰が）、および具体的な解消手段（どの会議体や手法で）という、解消に至るプロセスを具体的に明記している。</t>
+          <t>仕様書内の未確定（TBD）項目に対して、決定責任者、決定期限、および解決に至る具体的なアプローチをセットで明記している。</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】通信プロトコルの詳細が「後日決定（TBD）」とされたまま、具体的な解消の目途や期限が示されずに文書が完成とされている。（未決定事項の解消時期と方法が不明であるため）
-→【適合例】「通信プロトコルの詳細は、2024年10月末の設計定例会議にてベンダ提示の比較案に基づき、プロジェクトマネージャーが決定する（TBD）」と解消条件を記述する。</t>
+          <t>★新規追加
+【非適合例】外部連携APIのタイムアウト値はTBDとする。（未確定事項の解決プロセスおよび期限が記載されておらず、放置されるリスクがある。）
+→【適合例】外部連携APIのタイムアウト値はTBDとする。次回の定例会議にて、担当チームが負荷テスト結果に基づき数値を確定する。</t>
         </is>
       </c>
     </row>
